--- a/#AI_anonymized.xlsx
+++ b/#AI_anonymized.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7649,7 +7649,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7883,7 +7883,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13273,7 +13273,7 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13315,7 +13315,7 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13359,7 +13359,7 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18158,7 +18158,7 @@
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24443,7 +24443,7 @@
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24492,7 +24492,7 @@
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24578,7 +24578,7 @@
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29929,7 +29929,7 @@
       </c>
       <c r="J840" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29971,7 +29971,7 @@
       </c>
       <c r="J841" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36636,7 +36636,7 @@
       </c>
       <c r="J1040" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="J1041" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -42236,7 +42236,7 @@
       </c>
       <c r="J1199" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -42282,7 +42282,7 @@
       </c>
       <c r="J1200" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
